--- a/Documentacao/ModeloCronograma.xlsx
+++ b/Documentacao/ModeloCronograma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zbr96\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\newDownload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC90EB1B-CD56-4835-8EF8-A446A424F5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87860AAF-F788-42EE-9A5D-99ECD4FBB4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6312369C-9BF2-40D2-B40C-CD4356B33EFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6312369C-9BF2-40D2-B40C-CD4356B33EFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="28">
   <si>
     <t>ID Atividade</t>
   </si>
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,6 +134,14 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -230,6 +238,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -239,21 +256,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89DAB83-86DF-4309-B28F-F2BFD672B39D}">
-  <dimension ref="A1:CN42"/>
+  <dimension ref="A1:CN50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -583,390 +589,390 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="6">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="9">
         <v>44963</v>
       </c>
-      <c r="I1" s="6">
+      <c r="I1" s="9">
         <v>44964</v>
       </c>
-      <c r="J1" s="6">
+      <c r="J1" s="9">
         <v>44965</v>
       </c>
-      <c r="K1" s="6">
+      <c r="K1" s="9">
         <v>44966</v>
       </c>
-      <c r="L1" s="6">
+      <c r="L1" s="9">
         <v>44967</v>
       </c>
-      <c r="M1" s="6">
+      <c r="M1" s="9">
         <v>44998</v>
       </c>
-      <c r="N1" s="6">
+      <c r="N1" s="9">
         <v>44999</v>
       </c>
-      <c r="O1" s="6">
+      <c r="O1" s="9">
         <v>45000</v>
       </c>
-      <c r="P1" s="6">
+      <c r="P1" s="9">
         <v>45001</v>
       </c>
-      <c r="Q1" s="6">
+      <c r="Q1" s="9">
         <v>45002</v>
       </c>
-      <c r="R1" s="6">
+      <c r="R1" s="9">
         <v>45005</v>
       </c>
-      <c r="S1" s="6">
+      <c r="S1" s="9">
         <v>45006</v>
       </c>
-      <c r="T1" s="6">
+      <c r="T1" s="9">
         <v>45007</v>
       </c>
-      <c r="U1" s="6">
+      <c r="U1" s="9">
         <v>45008</v>
       </c>
-      <c r="V1" s="6">
+      <c r="V1" s="9">
         <v>45009</v>
       </c>
-      <c r="W1" s="6">
+      <c r="W1" s="9">
         <v>45012</v>
       </c>
-      <c r="X1" s="6">
+      <c r="X1" s="9">
         <v>45013</v>
       </c>
-      <c r="Y1" s="6">
+      <c r="Y1" s="9">
         <v>45014</v>
       </c>
-      <c r="Z1" s="6">
+      <c r="Z1" s="9">
         <v>45015</v>
       </c>
-      <c r="AA1" s="6">
+      <c r="AA1" s="9">
         <v>45016</v>
       </c>
-      <c r="AB1" s="6">
+      <c r="AB1" s="9">
         <v>45019</v>
       </c>
-      <c r="AC1" s="6">
+      <c r="AC1" s="9">
         <v>45020</v>
       </c>
-      <c r="AD1" s="6">
+      <c r="AD1" s="9">
         <v>45021</v>
       </c>
-      <c r="AE1" s="6">
+      <c r="AE1" s="9">
         <v>45022</v>
       </c>
-      <c r="AF1" s="6">
+      <c r="AF1" s="9">
         <v>45023</v>
       </c>
-      <c r="AG1" s="6">
+      <c r="AG1" s="9">
         <v>45026</v>
       </c>
-      <c r="AH1" s="6">
+      <c r="AH1" s="9">
         <v>45027</v>
       </c>
-      <c r="AI1" s="6">
+      <c r="AI1" s="9">
         <v>45028</v>
       </c>
-      <c r="AJ1" s="6">
+      <c r="AJ1" s="9">
         <v>45029</v>
       </c>
-      <c r="AK1" s="6">
+      <c r="AK1" s="9">
         <v>45030</v>
       </c>
-      <c r="AL1" s="6">
+      <c r="AL1" s="9">
         <v>45033</v>
       </c>
-      <c r="AM1" s="6">
+      <c r="AM1" s="9">
         <v>45034</v>
       </c>
-      <c r="AN1" s="6">
+      <c r="AN1" s="9">
         <v>45035</v>
       </c>
-      <c r="AO1" s="6">
+      <c r="AO1" s="9">
         <v>45036</v>
       </c>
-      <c r="AP1" s="6">
+      <c r="AP1" s="9">
         <v>45037</v>
       </c>
-      <c r="AQ1" s="6">
+      <c r="AQ1" s="9">
         <v>45040</v>
       </c>
-      <c r="AR1" s="6">
+      <c r="AR1" s="9">
         <v>45041</v>
       </c>
-      <c r="AS1" s="6">
+      <c r="AS1" s="9">
         <v>45042</v>
       </c>
-      <c r="AT1" s="6">
+      <c r="AT1" s="9">
         <v>45043</v>
       </c>
-      <c r="AU1" s="6">
+      <c r="AU1" s="9">
         <v>45044</v>
       </c>
-      <c r="AV1" s="6">
+      <c r="AV1" s="9">
         <v>45041</v>
       </c>
-      <c r="AW1" s="6">
+      <c r="AW1" s="9">
         <v>45042</v>
       </c>
-      <c r="AX1" s="6">
+      <c r="AX1" s="9">
         <v>45043</v>
       </c>
-      <c r="AY1" s="6">
+      <c r="AY1" s="9">
         <v>45044</v>
       </c>
-      <c r="AZ1" s="6">
+      <c r="AZ1" s="9">
         <v>45047</v>
       </c>
-      <c r="BA1" s="6">
+      <c r="BA1" s="9">
         <v>45048</v>
       </c>
-      <c r="BB1" s="6">
+      <c r="BB1" s="9">
         <v>45049</v>
       </c>
-      <c r="BC1" s="6">
+      <c r="BC1" s="9">
         <v>45050</v>
       </c>
-      <c r="BD1" s="6">
+      <c r="BD1" s="9">
         <v>45051</v>
       </c>
-      <c r="BE1" s="6">
+      <c r="BE1" s="9">
         <v>45054</v>
       </c>
-      <c r="BF1" s="6">
+      <c r="BF1" s="9">
         <v>45055</v>
       </c>
-      <c r="BG1" s="6">
+      <c r="BG1" s="9">
         <v>45056</v>
       </c>
-      <c r="BH1" s="6">
+      <c r="BH1" s="9">
         <v>45057</v>
       </c>
-      <c r="BI1" s="6">
+      <c r="BI1" s="9">
         <v>45058</v>
       </c>
-      <c r="BJ1" s="6">
+      <c r="BJ1" s="9">
         <v>45061</v>
       </c>
-      <c r="BK1" s="6">
+      <c r="BK1" s="9">
         <v>45062</v>
       </c>
-      <c r="BL1" s="6">
+      <c r="BL1" s="9">
         <v>45063</v>
       </c>
-      <c r="BM1" s="6">
+      <c r="BM1" s="9">
         <v>45064</v>
       </c>
-      <c r="BN1" s="6">
+      <c r="BN1" s="9">
         <v>45065</v>
       </c>
-      <c r="BO1" s="6">
+      <c r="BO1" s="9">
         <v>45068</v>
       </c>
-      <c r="BP1" s="6">
+      <c r="BP1" s="9">
         <v>45069</v>
       </c>
-      <c r="BQ1" s="6">
+      <c r="BQ1" s="9">
         <v>45070</v>
       </c>
-      <c r="BR1" s="6">
+      <c r="BR1" s="9">
         <v>45071</v>
       </c>
-      <c r="BS1" s="6">
+      <c r="BS1" s="9">
         <v>45072</v>
       </c>
-      <c r="BT1" s="6">
+      <c r="BT1" s="9">
         <v>45075</v>
       </c>
-      <c r="BU1" s="6">
+      <c r="BU1" s="9">
         <v>45076</v>
       </c>
-      <c r="BV1" s="6">
+      <c r="BV1" s="9">
         <v>45077</v>
       </c>
-      <c r="BW1" s="6">
+      <c r="BW1" s="9">
         <v>45078</v>
       </c>
-      <c r="BX1" s="6">
+      <c r="BX1" s="9">
         <v>45079</v>
       </c>
-      <c r="BY1" s="6">
+      <c r="BY1" s="9">
         <v>45082</v>
       </c>
-      <c r="BZ1" s="6">
+      <c r="BZ1" s="9">
         <v>45083</v>
       </c>
-      <c r="CA1" s="6">
+      <c r="CA1" s="9">
         <v>45084</v>
       </c>
-      <c r="CB1" s="6">
+      <c r="CB1" s="9">
         <v>45085</v>
       </c>
-      <c r="CC1" s="6">
+      <c r="CC1" s="9">
         <v>45086</v>
       </c>
-      <c r="CD1" s="6">
+      <c r="CD1" s="9">
         <v>45089</v>
       </c>
-      <c r="CE1" s="6">
+      <c r="CE1" s="9">
         <v>45090</v>
       </c>
-      <c r="CF1" s="6">
+      <c r="CF1" s="9">
         <v>45091</v>
       </c>
-      <c r="CG1" s="6">
+      <c r="CG1" s="9">
         <v>45092</v>
       </c>
-      <c r="CH1" s="6">
+      <c r="CH1" s="9">
         <v>45093</v>
       </c>
-      <c r="CI1" s="6">
+      <c r="CI1" s="9">
         <v>45096</v>
       </c>
-      <c r="CJ1" s="6">
+      <c r="CJ1" s="9">
         <v>45097</v>
       </c>
-      <c r="CK1" s="6">
+      <c r="CK1" s="9">
         <v>45098</v>
       </c>
-      <c r="CL1" s="6">
+      <c r="CL1" s="9">
         <v>45099</v>
       </c>
-      <c r="CM1" s="6">
+      <c r="CM1" s="9">
         <v>45100</v>
       </c>
-      <c r="CN1" s="6">
+      <c r="CN1" s="9">
         <v>45103</v>
       </c>
     </row>
     <row r="2" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="7"/>
-      <c r="AK2" s="7"/>
-      <c r="AL2" s="7"/>
-      <c r="AM2" s="7"/>
-      <c r="AN2" s="7"/>
-      <c r="AO2" s="7"/>
-      <c r="AP2" s="7"/>
-      <c r="AQ2" s="7"/>
-      <c r="AR2" s="7"/>
-      <c r="AS2" s="7"/>
-      <c r="AT2" s="7"/>
-      <c r="AU2" s="7"/>
-      <c r="AV2" s="7"/>
-      <c r="AW2" s="7"/>
-      <c r="AX2" s="7"/>
-      <c r="AY2" s="7"/>
-      <c r="AZ2" s="7"/>
-      <c r="BA2" s="7"/>
-      <c r="BB2" s="7"/>
-      <c r="BC2" s="7"/>
-      <c r="BD2" s="7"/>
-      <c r="BE2" s="7"/>
-      <c r="BF2" s="7"/>
-      <c r="BG2" s="7"/>
-      <c r="BH2" s="7"/>
-      <c r="BI2" s="7"/>
-      <c r="BJ2" s="7"/>
-      <c r="BK2" s="7"/>
-      <c r="BL2" s="7"/>
-      <c r="BM2" s="7"/>
-      <c r="BN2" s="7"/>
-      <c r="BO2" s="7"/>
-      <c r="BP2" s="7"/>
-      <c r="BQ2" s="7"/>
-      <c r="BR2" s="7"/>
-      <c r="BS2" s="7"/>
-      <c r="BT2" s="7"/>
-      <c r="BU2" s="7"/>
-      <c r="BV2" s="7"/>
-      <c r="BW2" s="7"/>
-      <c r="BX2" s="7"/>
-      <c r="BY2" s="7"/>
-      <c r="BZ2" s="7"/>
-      <c r="CA2" s="7"/>
-      <c r="CB2" s="7"/>
-      <c r="CC2" s="7"/>
-      <c r="CD2" s="7"/>
-      <c r="CE2" s="7"/>
-      <c r="CF2" s="7"/>
-      <c r="CG2" s="7"/>
-      <c r="CH2" s="7"/>
-      <c r="CI2" s="7"/>
-      <c r="CJ2" s="7"/>
-      <c r="CK2" s="7"/>
-      <c r="CL2" s="7"/>
-      <c r="CM2" s="7"/>
-      <c r="CN2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+      <c r="AN2" s="10"/>
+      <c r="AO2" s="10"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="10"/>
+      <c r="AW2" s="10"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="10"/>
+      <c r="BA2" s="10"/>
+      <c r="BB2" s="10"/>
+      <c r="BC2" s="10"/>
+      <c r="BD2" s="10"/>
+      <c r="BE2" s="10"/>
+      <c r="BF2" s="10"/>
+      <c r="BG2" s="10"/>
+      <c r="BH2" s="10"/>
+      <c r="BI2" s="10"/>
+      <c r="BJ2" s="10"/>
+      <c r="BK2" s="10"/>
+      <c r="BL2" s="10"/>
+      <c r="BM2" s="10"/>
+      <c r="BN2" s="10"/>
+      <c r="BO2" s="10"/>
+      <c r="BP2" s="10"/>
+      <c r="BQ2" s="10"/>
+      <c r="BR2" s="10"/>
+      <c r="BS2" s="10"/>
+      <c r="BT2" s="10"/>
+      <c r="BU2" s="10"/>
+      <c r="BV2" s="10"/>
+      <c r="BW2" s="10"/>
+      <c r="BX2" s="10"/>
+      <c r="BY2" s="10"/>
+      <c r="BZ2" s="10"/>
+      <c r="CA2" s="10"/>
+      <c r="CB2" s="10"/>
+      <c r="CC2" s="10"/>
+      <c r="CD2" s="10"/>
+      <c r="CE2" s="10"/>
+      <c r="CF2" s="10"/>
+      <c r="CG2" s="10"/>
+      <c r="CH2" s="10"/>
+      <c r="CI2" s="10"/>
+      <c r="CJ2" s="10"/>
+      <c r="CK2" s="10"/>
+      <c r="CL2" s="10"/>
+      <c r="CM2" s="10"/>
+      <c r="CN2" s="10"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="8">
         <v>46059</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="8">
         <v>46068</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1059,20 +1065,20 @@
       <c r="CN3" s="5"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -1155,20 +1161,20 @@
       <c r="CN4" s="5"/>
     </row>
     <row r="5" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="12">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="12">
         <v>1</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11">
+      <c r="D5" s="12"/>
+      <c r="E5" s="8">
         <v>46069</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>46081</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1261,12 +1267,12 @@
       <c r="CN5" s="5"/>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="G6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1274,7 +1280,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -1357,20 +1363,20 @@
       <c r="CN6" s="5"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="12">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11">
+      <c r="D7" s="12"/>
+      <c r="E7" s="8">
         <v>46082</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <v>46091</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1463,12 +1469,12 @@
       <c r="CN7" s="5"/>
     </row>
     <row r="8" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1477,7 +1483,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="4"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -1559,20 +1565,20 @@
       <c r="CN8" s="5"/>
     </row>
     <row r="9" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="12">
         <v>3</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11">
+      <c r="D9" s="12"/>
+      <c r="E9" s="8">
         <v>46092</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <v>46101</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1665,12 +1671,12 @@
       <c r="CN9" s="5"/>
     </row>
     <row r="10" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1679,12 +1685,12 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
@@ -1761,20 +1767,20 @@
       <c r="CN10" s="5"/>
     </row>
     <row r="11" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="12">
         <v>5</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="12">
         <v>4</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11">
+      <c r="D11" s="12"/>
+      <c r="E11" s="8">
         <v>46102</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <v>46112</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1867,12 +1873,12 @@
       <c r="CN11" s="5"/>
     </row>
     <row r="12" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1887,15 +1893,15 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
@@ -1963,20 +1969,20 @@
       <c r="CN12" s="5"/>
     </row>
     <row r="13" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="12">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="12">
         <v>4</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11">
+      <c r="D13" s="12"/>
+      <c r="E13" s="8">
         <v>46113</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>46122</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -2069,12 +2075,12 @@
       <c r="CN13" s="5"/>
     </row>
     <row r="14" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="2" t="s">
         <v>7</v>
       </c>
@@ -2098,12 +2104,12 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="5"/>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
@@ -2165,20 +2171,20 @@
       <c r="CN14" s="5"/>
     </row>
     <row r="15" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="12">
         <v>7</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="12">
         <v>4</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11">
+      <c r="D15" s="12"/>
+      <c r="E15" s="8">
         <v>46123</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="8">
         <v>46132</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -2271,12 +2277,12 @@
       <c r="CN15" s="5"/>
     </row>
     <row r="16" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2306,14 +2312,14 @@
       <c r="AE16" s="5"/>
       <c r="AF16" s="5"/>
       <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="5"/>
-      <c r="AJ16" s="5"/>
-      <c r="AK16" s="5"/>
-      <c r="AL16" s="5"/>
-      <c r="AM16" s="5"/>
-      <c r="AN16" s="5"/>
-      <c r="AO16" s="5"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
       <c r="AP16" s="5"/>
       <c r="AQ16" s="5"/>
       <c r="AR16" s="5"/>
@@ -2367,20 +2373,20 @@
       <c r="CN16" s="5"/>
     </row>
     <row r="17" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="12">
         <v>8</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="12">
         <v>4</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11">
+      <c r="D17" s="12"/>
+      <c r="E17" s="8">
         <v>46133</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <v>46140</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -2473,12 +2479,12 @@
       <c r="CN17" s="5"/>
     </row>
     <row r="18" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2516,16 +2522,16 @@
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
       <c r="AO18" s="5"/>
-      <c r="AP18" s="5"/>
-      <c r="AQ18" s="5"/>
-      <c r="AR18" s="5"/>
-      <c r="AS18" s="5"/>
-      <c r="AT18" s="5"/>
-      <c r="AU18" s="5"/>
-      <c r="AV18" s="5"/>
-      <c r="AW18" s="5"/>
-      <c r="AX18" s="5"/>
-      <c r="AY18" s="5"/>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="4"/>
+      <c r="AR18" s="4"/>
+      <c r="AS18" s="4"/>
+      <c r="AT18" s="4"/>
+      <c r="AU18" s="4"/>
+      <c r="AV18" s="4"/>
+      <c r="AW18" s="4"/>
+      <c r="AX18" s="4"/>
+      <c r="AY18" s="4"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="5"/>
       <c r="BB18" s="5"/>
@@ -2569,20 +2575,20 @@
       <c r="CN18" s="5"/>
     </row>
     <row r="19" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="12">
         <v>9</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="12">
         <v>4</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11">
+      <c r="D19" s="12"/>
+      <c r="E19" s="8">
         <v>46143</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>46150</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2675,12 +2681,12 @@
       <c r="CN19" s="5"/>
     </row>
     <row r="20" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2728,12 +2734,12 @@
       <c r="AW20" s="5"/>
       <c r="AX20" s="5"/>
       <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
       <c r="BF20" s="5"/>
       <c r="BG20" s="5"/>
       <c r="BH20" s="5"/>
@@ -2771,20 +2777,20 @@
       <c r="CN20" s="5"/>
     </row>
     <row r="21" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="12">
         <v>10</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11">
+      <c r="D21" s="12"/>
+      <c r="E21" s="8">
         <v>46151</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="8">
         <v>46160</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2877,12 +2883,12 @@
       <c r="CN21" s="5"/>
     </row>
     <row r="22" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="2" t="s">
         <v>7</v>
       </c>
@@ -2936,14 +2942,14 @@
       <c r="BC22" s="5"/>
       <c r="BD22" s="5"/>
       <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BH22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="4"/>
       <c r="BN22" s="5"/>
       <c r="BO22" s="5"/>
       <c r="BP22" s="5"/>
@@ -2973,20 +2979,20 @@
       <c r="CN22" s="5"/>
     </row>
     <row r="23" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="12">
         <v>11</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="12">
         <v>10</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11">
+      <c r="D23" s="12"/>
+      <c r="E23" s="8">
         <v>46161</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <v>46170</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -3079,12 +3085,12 @@
       <c r="CN23" s="5"/>
     </row>
     <row r="24" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="2" t="s">
         <v>7</v>
       </c>
@@ -3146,13 +3152,13 @@
       <c r="BK24" s="5"/>
       <c r="BL24" s="5"/>
       <c r="BM24" s="5"/>
-      <c r="BN24" s="5"/>
-      <c r="BO24" s="5"/>
-      <c r="BP24" s="5"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="5"/>
-      <c r="BS24" s="5"/>
-      <c r="BT24" s="5"/>
+      <c r="BN24" s="4"/>
+      <c r="BO24" s="4"/>
+      <c r="BP24" s="4"/>
+      <c r="BQ24" s="4"/>
+      <c r="BR24" s="4"/>
+      <c r="BS24" s="4"/>
+      <c r="BT24" s="4"/>
       <c r="BU24" s="5"/>
       <c r="BV24" s="5"/>
       <c r="BW24" s="5"/>
@@ -3175,20 +3181,20 @@
       <c r="CN24" s="5"/>
     </row>
     <row r="25" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="12">
         <v>12</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="12">
         <v>10</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11">
+      <c r="D25" s="12"/>
+      <c r="E25" s="8">
         <v>46171</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="8">
         <v>46178</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -3281,12 +3287,12 @@
       <c r="CN25" s="5"/>
     </row>
     <row r="26" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="2" t="s">
         <v>7</v>
       </c>
@@ -3354,12 +3360,12 @@
       <c r="BQ26" s="5"/>
       <c r="BR26" s="5"/>
       <c r="BS26" s="5"/>
-      <c r="BT26" s="5"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="5"/>
-      <c r="BW26" s="5"/>
-      <c r="BX26" s="5"/>
-      <c r="BY26" s="5"/>
+      <c r="BT26" s="4"/>
+      <c r="BU26" s="4"/>
+      <c r="BV26" s="4"/>
+      <c r="BW26" s="4"/>
+      <c r="BX26" s="4"/>
+      <c r="BY26" s="4"/>
       <c r="BZ26" s="5"/>
       <c r="CA26" s="5"/>
       <c r="CB26" s="5"/>
@@ -3377,20 +3383,20 @@
       <c r="CN26" s="5"/>
     </row>
     <row r="27" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="12">
         <v>13</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="12">
         <v>10</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11">
+      <c r="D27" s="12"/>
+      <c r="E27" s="8">
         <v>46179</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="8">
         <v>46185</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -3483,12 +3489,12 @@
       <c r="CN27" s="5"/>
     </row>
     <row r="28" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="2" t="s">
         <v>7</v>
       </c>
@@ -3562,11 +3568,11 @@
       <c r="BW28" s="5"/>
       <c r="BX28" s="5"/>
       <c r="BY28" s="5"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="5"/>
-      <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
-      <c r="CD28" s="5"/>
+      <c r="BZ28" s="4"/>
+      <c r="CA28" s="4"/>
+      <c r="CB28" s="4"/>
+      <c r="CC28" s="4"/>
+      <c r="CD28" s="4"/>
       <c r="CE28" s="5"/>
       <c r="CF28" s="5"/>
       <c r="CG28" s="5"/>
@@ -3579,20 +3585,20 @@
       <c r="CN28" s="5"/>
     </row>
     <row r="29" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="12">
         <v>14</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11">
+      <c r="D29" s="12"/>
+      <c r="E29" s="8">
         <v>46186</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="8">
         <v>46191</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -3685,12 +3691,12 @@
       <c r="CN29" s="5"/>
     </row>
     <row r="30" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="2" t="s">
         <v>7</v>
       </c>
@@ -3769,11 +3775,11 @@
       <c r="CB30" s="5"/>
       <c r="CC30" s="5"/>
       <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
+      <c r="CE30" s="4"/>
+      <c r="CF30" s="4"/>
+      <c r="CG30" s="4"/>
+      <c r="CH30" s="4"/>
+      <c r="CI30" s="4"/>
       <c r="CJ30" s="5"/>
       <c r="CK30" s="5"/>
       <c r="CL30" s="5"/>
@@ -3781,20 +3787,20 @@
       <c r="CN30" s="5"/>
     </row>
     <row r="31" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="12">
         <v>15</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="12">
         <v>14</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11">
+      <c r="D31" s="12"/>
+      <c r="E31" s="8">
         <v>46192</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="8">
         <v>46194</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -3887,12 +3893,12 @@
       <c r="CN31" s="5"/>
     </row>
     <row r="32" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="2" t="s">
         <v>7</v>
       </c>
@@ -3975,28 +3981,28 @@
       <c r="CF32" s="5"/>
       <c r="CG32" s="5"/>
       <c r="CH32" s="5"/>
-      <c r="CI32" s="5"/>
-      <c r="CJ32" s="5"/>
-      <c r="CK32" s="5"/>
+      <c r="CI32" s="4"/>
+      <c r="CJ32" s="4"/>
+      <c r="CK32" s="4"/>
       <c r="CL32" s="5"/>
       <c r="CM32" s="5"/>
       <c r="CN32" s="5"/>
     </row>
     <row r="33" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="A33" s="12">
         <v>16</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="12">
         <v>14</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11">
+      <c r="D33" s="12"/>
+      <c r="E33" s="8">
         <v>46195</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="8">
         <v>46197</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -4089,12 +4095,12 @@
       <c r="CN33" s="5"/>
     </row>
     <row r="34" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="2" t="s">
         <v>7</v>
       </c>
@@ -4180,25 +4186,25 @@
       <c r="CI34" s="5"/>
       <c r="CJ34" s="5"/>
       <c r="CK34" s="5"/>
-      <c r="CL34" s="5"/>
-      <c r="CM34" s="5"/>
+      <c r="CL34" s="4"/>
+      <c r="CM34" s="4"/>
       <c r="CN34" s="5"/>
     </row>
     <row r="35" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+      <c r="A35" s="12">
         <v>17</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="12">
         <v>16</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="11">
+      <c r="D35" s="12"/>
+      <c r="E35" s="8">
         <v>46198</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="8">
         <v>46199</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -4291,12 +4297,12 @@
       <c r="CN35" s="3"/>
     </row>
     <row r="36" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="2" t="s">
         <v>7</v>
       </c>
@@ -4384,630 +4390,145 @@
       <c r="CK36" s="5"/>
       <c r="CL36" s="5"/>
       <c r="CM36" s="5"/>
-      <c r="CN36" s="5"/>
+      <c r="CN36" s="4"/>
     </row>
-    <row r="37" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
-        <v>18</v>
-      </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-      <c r="U37" s="5"/>
-      <c r="V37" s="5"/>
-      <c r="W37" s="5"/>
-      <c r="X37" s="5"/>
-      <c r="Y37" s="5"/>
-      <c r="Z37" s="5"/>
-      <c r="AA37" s="5"/>
-      <c r="AB37" s="5"/>
-      <c r="AC37" s="5"/>
-      <c r="AD37" s="5"/>
-      <c r="AE37" s="5"/>
-      <c r="AF37" s="5"/>
-      <c r="AG37" s="5"/>
-      <c r="AH37" s="5"/>
-      <c r="AI37" s="5"/>
-      <c r="AJ37" s="5"/>
-      <c r="AK37" s="5"/>
-      <c r="AL37" s="5"/>
-      <c r="AM37" s="5"/>
-      <c r="AN37" s="5"/>
-      <c r="AO37" s="5"/>
-      <c r="AP37" s="5"/>
-      <c r="AQ37" s="5"/>
-      <c r="AR37" s="5"/>
-      <c r="AS37" s="5"/>
-      <c r="AT37" s="5"/>
-      <c r="AU37" s="5"/>
-      <c r="AV37" s="5"/>
-      <c r="AW37" s="5"/>
-      <c r="AX37" s="5"/>
-      <c r="AY37" s="5"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="5"/>
-      <c r="BB37" s="5"/>
-      <c r="BC37" s="5"/>
-      <c r="BD37" s="5"/>
-      <c r="BE37" s="5"/>
-      <c r="BF37" s="5"/>
-      <c r="BG37" s="5"/>
-      <c r="BH37" s="5"/>
-      <c r="BI37" s="5"/>
-      <c r="BJ37" s="5"/>
-      <c r="BK37" s="5"/>
-      <c r="BL37" s="5"/>
-      <c r="BM37" s="5"/>
-      <c r="BN37" s="5"/>
-      <c r="BO37" s="5"/>
-      <c r="BP37" s="5"/>
-      <c r="BQ37" s="5"/>
-      <c r="BR37" s="5"/>
-      <c r="BS37" s="5"/>
-      <c r="BT37" s="5"/>
-      <c r="BU37" s="5"/>
-      <c r="BV37" s="5"/>
-      <c r="BW37" s="5"/>
-      <c r="BX37" s="5"/>
-      <c r="BY37" s="5"/>
-      <c r="BZ37" s="5"/>
-      <c r="CA37" s="5"/>
-      <c r="CB37" s="5"/>
-      <c r="CC37" s="5"/>
-      <c r="CD37" s="5"/>
-      <c r="CE37" s="5"/>
-      <c r="CF37" s="5"/>
-      <c r="CG37" s="5"/>
-      <c r="CH37" s="5"/>
-      <c r="CI37" s="5"/>
-      <c r="CJ37" s="5"/>
-      <c r="CK37" s="5"/>
-      <c r="CL37" s="5"/>
-      <c r="CM37" s="5"/>
-      <c r="CN37" s="5"/>
-    </row>
-    <row r="38" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
-      <c r="V38" s="5"/>
-      <c r="W38" s="5"/>
-      <c r="X38" s="5"/>
-      <c r="Y38" s="5"/>
-      <c r="Z38" s="5"/>
-      <c r="AA38" s="5"/>
-      <c r="AB38" s="5"/>
-      <c r="AC38" s="5"/>
-      <c r="AD38" s="5"/>
-      <c r="AE38" s="5"/>
-      <c r="AF38" s="5"/>
-      <c r="AG38" s="5"/>
-      <c r="AH38" s="5"/>
-      <c r="AI38" s="5"/>
-      <c r="AJ38" s="5"/>
-      <c r="AK38" s="5"/>
-      <c r="AL38" s="5"/>
-      <c r="AM38" s="5"/>
-      <c r="AN38" s="5"/>
-      <c r="AO38" s="5"/>
-      <c r="AP38" s="5"/>
-      <c r="AQ38" s="5"/>
-      <c r="AR38" s="5"/>
-      <c r="AS38" s="5"/>
-      <c r="AT38" s="5"/>
-      <c r="AU38" s="5"/>
-      <c r="AV38" s="5"/>
-      <c r="AW38" s="5"/>
-      <c r="AX38" s="5"/>
-      <c r="AY38" s="5"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="5"/>
-      <c r="BB38" s="5"/>
-      <c r="BC38" s="5"/>
-      <c r="BD38" s="5"/>
-      <c r="BE38" s="5"/>
-      <c r="BF38" s="5"/>
-      <c r="BG38" s="5"/>
-      <c r="BH38" s="5"/>
-      <c r="BI38" s="5"/>
-      <c r="BJ38" s="5"/>
-      <c r="BK38" s="5"/>
-      <c r="BL38" s="5"/>
-      <c r="BM38" s="5"/>
-      <c r="BN38" s="5"/>
-      <c r="BO38" s="5"/>
-      <c r="BP38" s="5"/>
-      <c r="BQ38" s="5"/>
-      <c r="BR38" s="5"/>
-      <c r="BS38" s="5"/>
-      <c r="BT38" s="5"/>
-      <c r="BU38" s="5"/>
-      <c r="BV38" s="5"/>
-      <c r="BW38" s="5"/>
-      <c r="BX38" s="5"/>
-      <c r="BY38" s="5"/>
-      <c r="BZ38" s="5"/>
-      <c r="CA38" s="5"/>
-      <c r="CB38" s="5"/>
-      <c r="CC38" s="5"/>
-      <c r="CD38" s="5"/>
-      <c r="CE38" s="5"/>
-      <c r="CF38" s="5"/>
-      <c r="CG38" s="5"/>
-      <c r="CH38" s="5"/>
-      <c r="CI38" s="5"/>
-      <c r="CJ38" s="5"/>
-      <c r="CK38" s="5"/>
-      <c r="CL38" s="5"/>
-      <c r="CM38" s="5"/>
-      <c r="CN38" s="5"/>
-    </row>
-    <row r="39" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
-        <v>19</v>
-      </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
-      <c r="V39" s="5"/>
-      <c r="W39" s="5"/>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5"/>
-      <c r="Z39" s="5"/>
-      <c r="AA39" s="5"/>
-      <c r="AB39" s="5"/>
-      <c r="AC39" s="5"/>
-      <c r="AD39" s="5"/>
-      <c r="AE39" s="5"/>
-      <c r="AF39" s="5"/>
-      <c r="AG39" s="5"/>
-      <c r="AH39" s="5"/>
-      <c r="AI39" s="5"/>
-      <c r="AJ39" s="5"/>
-      <c r="AK39" s="5"/>
-      <c r="AL39" s="5"/>
-      <c r="AM39" s="5"/>
-      <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
-      <c r="AP39" s="5"/>
-      <c r="AQ39" s="5"/>
-      <c r="AR39" s="5"/>
-      <c r="AS39" s="5"/>
-      <c r="AT39" s="5"/>
-      <c r="AU39" s="5"/>
-      <c r="AV39" s="5"/>
-      <c r="AW39" s="5"/>
-      <c r="AX39" s="5"/>
-      <c r="AY39" s="5"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="5"/>
-      <c r="BB39" s="5"/>
-      <c r="BC39" s="5"/>
-      <c r="BD39" s="5"/>
-      <c r="BE39" s="5"/>
-      <c r="BF39" s="5"/>
-      <c r="BG39" s="5"/>
-      <c r="BH39" s="5"/>
-      <c r="BI39" s="5"/>
-      <c r="BJ39" s="5"/>
-      <c r="BK39" s="5"/>
-      <c r="BL39" s="5"/>
-      <c r="BM39" s="5"/>
-      <c r="BN39" s="5"/>
-      <c r="BO39" s="5"/>
-      <c r="BP39" s="5"/>
-      <c r="BQ39" s="5"/>
-      <c r="BR39" s="5"/>
-      <c r="BS39" s="5"/>
-      <c r="BT39" s="5"/>
-      <c r="BU39" s="5"/>
-      <c r="BV39" s="5"/>
-      <c r="BW39" s="5"/>
-      <c r="BX39" s="5"/>
-      <c r="BY39" s="5"/>
-      <c r="BZ39" s="5"/>
-      <c r="CA39" s="5"/>
-      <c r="CB39" s="5"/>
-      <c r="CC39" s="5"/>
-      <c r="CD39" s="5"/>
-      <c r="CE39" s="5"/>
-      <c r="CF39" s="5"/>
-      <c r="CG39" s="5"/>
-      <c r="CH39" s="5"/>
-      <c r="CI39" s="5"/>
-      <c r="CJ39" s="5"/>
-      <c r="CK39" s="5"/>
-      <c r="CL39" s="5"/>
-      <c r="CM39" s="5"/>
-      <c r="CN39" s="5"/>
-    </row>
-    <row r="40" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="5"/>
-      <c r="W40" s="5"/>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5"/>
-      <c r="Z40" s="5"/>
-      <c r="AA40" s="5"/>
-      <c r="AB40" s="5"/>
-      <c r="AC40" s="5"/>
-      <c r="AD40" s="5"/>
-      <c r="AE40" s="5"/>
-      <c r="AF40" s="5"/>
-      <c r="AG40" s="5"/>
-      <c r="AH40" s="5"/>
-      <c r="AI40" s="5"/>
-      <c r="AJ40" s="5"/>
-      <c r="AK40" s="5"/>
-      <c r="AL40" s="5"/>
-      <c r="AM40" s="5"/>
-      <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
-      <c r="AP40" s="5"/>
-      <c r="AQ40" s="5"/>
-      <c r="AR40" s="5"/>
-      <c r="AS40" s="5"/>
-      <c r="AT40" s="5"/>
-      <c r="AU40" s="5"/>
-      <c r="AV40" s="5"/>
-      <c r="AW40" s="5"/>
-      <c r="AX40" s="5"/>
-      <c r="AY40" s="5"/>
-      <c r="AZ40" s="5"/>
-      <c r="BA40" s="5"/>
-      <c r="BB40" s="5"/>
-      <c r="BC40" s="5"/>
-      <c r="BD40" s="5"/>
-      <c r="BE40" s="5"/>
-      <c r="BF40" s="5"/>
-      <c r="BG40" s="5"/>
-      <c r="BH40" s="5"/>
-      <c r="BI40" s="5"/>
-      <c r="BJ40" s="5"/>
-      <c r="BK40" s="5"/>
-      <c r="BL40" s="5"/>
-      <c r="BM40" s="5"/>
-      <c r="BN40" s="5"/>
-      <c r="BO40" s="5"/>
-      <c r="BP40" s="5"/>
-      <c r="BQ40" s="5"/>
-      <c r="BR40" s="5"/>
-      <c r="BS40" s="5"/>
-      <c r="BT40" s="5"/>
-      <c r="BU40" s="5"/>
-      <c r="BV40" s="5"/>
-      <c r="BW40" s="5"/>
-      <c r="BX40" s="5"/>
-      <c r="BY40" s="5"/>
-      <c r="BZ40" s="5"/>
-      <c r="CA40" s="5"/>
-      <c r="CB40" s="5"/>
-      <c r="CC40" s="5"/>
-      <c r="CD40" s="5"/>
-      <c r="CE40" s="5"/>
-      <c r="CF40" s="5"/>
-      <c r="CG40" s="5"/>
-      <c r="CH40" s="5"/>
-      <c r="CI40" s="5"/>
-      <c r="CJ40" s="5"/>
-      <c r="CK40" s="5"/>
-      <c r="CL40" s="5"/>
-      <c r="CM40" s="5"/>
-      <c r="CN40" s="5"/>
-    </row>
-    <row r="41" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
-        <v>20</v>
-      </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="5"/>
-      <c r="W41" s="5"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5"/>
-      <c r="Z41" s="5"/>
-      <c r="AA41" s="5"/>
-      <c r="AB41" s="5"/>
-      <c r="AC41" s="5"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="5"/>
-      <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
-      <c r="AH41" s="5"/>
-      <c r="AI41" s="5"/>
-      <c r="AJ41" s="5"/>
-      <c r="AK41" s="5"/>
-      <c r="AL41" s="5"/>
-      <c r="AM41" s="5"/>
-      <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
-      <c r="AP41" s="5"/>
-      <c r="AQ41" s="5"/>
-      <c r="AR41" s="5"/>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
-      <c r="AU41" s="5"/>
-      <c r="AV41" s="5"/>
-      <c r="AW41" s="5"/>
-      <c r="AX41" s="5"/>
-      <c r="AY41" s="5"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="5"/>
-      <c r="BB41" s="5"/>
-      <c r="BC41" s="5"/>
-      <c r="BD41" s="5"/>
-      <c r="BE41" s="5"/>
-      <c r="BF41" s="5"/>
-      <c r="BG41" s="5"/>
-      <c r="BH41" s="5"/>
-      <c r="BI41" s="5"/>
-      <c r="BJ41" s="5"/>
-      <c r="BK41" s="5"/>
-      <c r="BL41" s="5"/>
-      <c r="BM41" s="5"/>
-      <c r="BN41" s="5"/>
-      <c r="BO41" s="5"/>
-      <c r="BP41" s="5"/>
-      <c r="BQ41" s="5"/>
-      <c r="BR41" s="5"/>
-      <c r="BS41" s="5"/>
-      <c r="BT41" s="5"/>
-      <c r="BU41" s="5"/>
-      <c r="BV41" s="5"/>
-      <c r="BW41" s="5"/>
-      <c r="BX41" s="5"/>
-      <c r="BY41" s="5"/>
-      <c r="BZ41" s="5"/>
-      <c r="CA41" s="5"/>
-      <c r="CB41" s="5"/>
-      <c r="CC41" s="5"/>
-      <c r="CD41" s="5"/>
-      <c r="CE41" s="5"/>
-      <c r="CF41" s="5"/>
-      <c r="CG41" s="5"/>
-      <c r="CH41" s="5"/>
-      <c r="CI41" s="5"/>
-      <c r="CJ41" s="5"/>
-      <c r="CK41" s="5"/>
-      <c r="CL41" s="5"/>
-      <c r="CM41" s="5"/>
-      <c r="CN41" s="5"/>
-    </row>
-    <row r="42" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="5"/>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5"/>
-      <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
-      <c r="AB42" s="5"/>
-      <c r="AC42" s="5"/>
-      <c r="AD42" s="5"/>
-      <c r="AE42" s="5"/>
-      <c r="AF42" s="5"/>
-      <c r="AG42" s="5"/>
-      <c r="AH42" s="5"/>
-      <c r="AI42" s="5"/>
-      <c r="AJ42" s="5"/>
-      <c r="AK42" s="5"/>
-      <c r="AL42" s="5"/>
-      <c r="AM42" s="5"/>
-      <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
-      <c r="AP42" s="5"/>
-      <c r="AQ42" s="5"/>
-      <c r="AR42" s="5"/>
-      <c r="AS42" s="5"/>
-      <c r="AT42" s="5"/>
-      <c r="AU42" s="5"/>
-      <c r="AV42" s="5"/>
-      <c r="AW42" s="5"/>
-      <c r="AX42" s="5"/>
-      <c r="AY42" s="5"/>
-      <c r="AZ42" s="5"/>
-      <c r="BA42" s="5"/>
-      <c r="BB42" s="5"/>
-      <c r="BC42" s="5"/>
-      <c r="BD42" s="5"/>
-      <c r="BE42" s="5"/>
-      <c r="BF42" s="5"/>
-      <c r="BG42" s="5"/>
-      <c r="BH42" s="5"/>
-      <c r="BI42" s="5"/>
-      <c r="BJ42" s="5"/>
-      <c r="BK42" s="5"/>
-      <c r="BL42" s="5"/>
-      <c r="BM42" s="5"/>
-      <c r="BN42" s="5"/>
-      <c r="BO42" s="5"/>
-      <c r="BP42" s="5"/>
-      <c r="BQ42" s="5"/>
-      <c r="BR42" s="5"/>
-      <c r="BS42" s="5"/>
-      <c r="BT42" s="5"/>
-      <c r="BU42" s="5"/>
-      <c r="BV42" s="5"/>
-      <c r="BW42" s="5"/>
-      <c r="BX42" s="5"/>
-      <c r="BY42" s="5"/>
-      <c r="BZ42" s="5"/>
-      <c r="CA42" s="5"/>
-      <c r="CB42" s="5"/>
-      <c r="CC42" s="5"/>
-      <c r="CD42" s="5"/>
-      <c r="CE42" s="5"/>
-      <c r="CF42" s="5"/>
-      <c r="CG42" s="5"/>
-      <c r="CH42" s="5"/>
-      <c r="CI42" s="5"/>
-      <c r="CJ42" s="5"/>
-      <c r="CK42" s="5"/>
-      <c r="CL42" s="5"/>
-      <c r="CM42" s="5"/>
-      <c r="CN42" s="5"/>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="206">
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
+  <mergeCells count="188">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AQ1:AQ2"/>
+    <mergeCell ref="AR1:AR2"/>
+    <mergeCell ref="AS1:AS2"/>
+    <mergeCell ref="AT1:AT2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AC1:AC2"/>
+    <mergeCell ref="AD1:AD2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="AF1:AF2"/>
+    <mergeCell ref="AG1:AG2"/>
+    <mergeCell ref="AH1:AH2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="BA1:BA2"/>
+    <mergeCell ref="BB1:BB2"/>
+    <mergeCell ref="BC1:BC2"/>
+    <mergeCell ref="BD1:BD2"/>
+    <mergeCell ref="BE1:BE2"/>
+    <mergeCell ref="BF1:BF2"/>
+    <mergeCell ref="AU1:AU2"/>
+    <mergeCell ref="AV1:AV2"/>
+    <mergeCell ref="AW1:AW2"/>
+    <mergeCell ref="AX1:AX2"/>
+    <mergeCell ref="AY1:AY2"/>
+    <mergeCell ref="AZ1:AZ2"/>
+    <mergeCell ref="BM1:BM2"/>
+    <mergeCell ref="BN1:BN2"/>
+    <mergeCell ref="BO1:BO2"/>
+    <mergeCell ref="BP1:BP2"/>
+    <mergeCell ref="BQ1:BQ2"/>
+    <mergeCell ref="BR1:BR2"/>
+    <mergeCell ref="BG1:BG2"/>
+    <mergeCell ref="BH1:BH2"/>
+    <mergeCell ref="BI1:BI2"/>
+    <mergeCell ref="BJ1:BJ2"/>
+    <mergeCell ref="BK1:BK2"/>
+    <mergeCell ref="BL1:BL2"/>
     <mergeCell ref="CK1:CK2"/>
     <mergeCell ref="CL1:CL2"/>
     <mergeCell ref="CM1:CM2"/>
@@ -5032,150 +4553,38 @@
     <mergeCell ref="BW1:BW2"/>
     <mergeCell ref="BX1:BX2"/>
     <mergeCell ref="BY1:BY2"/>
-    <mergeCell ref="BM1:BM2"/>
-    <mergeCell ref="BN1:BN2"/>
-    <mergeCell ref="BO1:BO2"/>
-    <mergeCell ref="BP1:BP2"/>
-    <mergeCell ref="BQ1:BQ2"/>
-    <mergeCell ref="BR1:BR2"/>
-    <mergeCell ref="BG1:BG2"/>
-    <mergeCell ref="BH1:BH2"/>
-    <mergeCell ref="BI1:BI2"/>
-    <mergeCell ref="BJ1:BJ2"/>
-    <mergeCell ref="BK1:BK2"/>
-    <mergeCell ref="BL1:BL2"/>
-    <mergeCell ref="BA1:BA2"/>
-    <mergeCell ref="BB1:BB2"/>
-    <mergeCell ref="BC1:BC2"/>
-    <mergeCell ref="BD1:BD2"/>
-    <mergeCell ref="BE1:BE2"/>
-    <mergeCell ref="BF1:BF2"/>
-    <mergeCell ref="AU1:AU2"/>
-    <mergeCell ref="AV1:AV2"/>
-    <mergeCell ref="AW1:AW2"/>
-    <mergeCell ref="AX1:AX2"/>
-    <mergeCell ref="AY1:AY2"/>
-    <mergeCell ref="AZ1:AZ2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AQ1:AQ2"/>
-    <mergeCell ref="AR1:AR2"/>
-    <mergeCell ref="AS1:AS2"/>
-    <mergeCell ref="AT1:AT2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AC1:AC2"/>
-    <mergeCell ref="AD1:AD2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
-    <mergeCell ref="AE1:AE2"/>
-    <mergeCell ref="AF1:AF2"/>
-    <mergeCell ref="AG1:AG2"/>
-    <mergeCell ref="AH1:AH2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
